--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1161,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,685 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1066,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1130,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1137,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1363,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1513,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1585,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1624,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1696,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1807,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1861,7 +1885,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2091,7 +2115,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2176,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2263,7 +2287,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2307,11 +2331,582 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr"/>
-      <c r="AC16" s="2" t="inlineStr">
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>—/11</t>
         </is>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1465,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1522,17 +1526,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1542,13 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1576,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1609,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1633,17 +1645,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1653,13 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1687,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1720,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1798,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1831,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1855,17 +1883,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1875,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1985,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2061,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2100,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2176,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2287,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2402,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2517,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2632,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2747,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2791,13 +2819,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2805,22 +2837,22 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2853,12 +2885,12 @@
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2872,43 +2904,392 @@
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr">
         <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>08:50</t>
         </is>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W21" s="2" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z21" s="2" t="inlineStr">
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>—/11</t>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1713,19 +1713,19 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1941,32 +1941,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1974,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,17 +2002,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2018,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2056,32 +2060,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2089,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2113,17 +2121,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2133,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2171,32 +2179,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2204,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2228,33 +2240,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2282,32 +2298,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2315,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2339,32 +2359,32 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2397,32 +2417,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2430,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2454,37 +2478,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2512,32 +2536,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2545,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2569,37 +2597,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2627,32 +2655,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2660,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2684,32 +2716,32 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2742,32 +2774,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2775,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2799,17 +2835,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2819,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2929,7 +2965,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2939,7 +2975,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3005,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3080,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3059,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3164,12 +3200,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3182,22 +3218,22 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3230,12 +3266,12 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3249,45 +3285,850 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>09:18</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
         <is>
           <t>7/11</t>
         </is>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2784,24 +2784,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2893,32 +2893,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,17 +2954,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2970,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3008,32 +3012,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3041,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3065,17 +3073,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3085,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3123,32 +3131,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3156,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3180,17 +3192,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3200,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3238,32 +3250,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3271,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3295,37 +3311,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3369,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3386,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3410,37 +3430,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3555,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3583,32 +3603,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3616,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3640,37 +3664,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3909,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3961,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4005,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4120,17 +4144,592 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>70.7</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,14 +2017,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>70.7</t>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>70.7</t>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3260,24 +3260,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3488,32 +3488,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3521,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,37 +3549,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3613,24 +3617,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3640,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,7 +3693,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3722,32 +3726,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3755,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3779,17 +3787,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3799,17 +3807,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3924,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3952,32 +3960,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3985,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4021,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4029,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4067,32 +4079,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4100,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4124,37 +4140,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4182,32 +4198,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4215,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4239,17 +4259,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4259,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,7 +4389,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4379,12 +4399,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4494,7 +4514,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4560,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4675,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4729,7 +4749,467 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3922,17 +3922,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4089,24 +4089,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4208,24 +4208,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4317,32 +4317,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -4350,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,17 +4378,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4394,17 +4398,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4432,32 +4436,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4465,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4489,17 +4497,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4509,17 +4517,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,7 +4627,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4662,32 +4670,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -4695,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4719,17 +4731,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4739,17 +4751,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,7 +4861,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4864,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4974,12 +4986,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5094,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5199,17 +5211,477 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>77.5</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>9/11</t>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC44"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>73.2</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,14 +2136,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>73.2</t>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,17 +2493,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,14 +3445,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>73.2</t>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,14 +4274,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>73.2</t>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4555,32 +4555,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4588,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,17 +4616,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4632,17 +4636,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4670,36 +4674,32 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,37 +4731,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4789,32 +4789,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4822,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4846,17 +4850,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4866,12 +4870,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4904,32 +4908,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4937,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4961,17 +4969,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4981,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5019,32 +5027,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5052,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5076,32 +5088,32 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5134,32 +5146,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5167,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5191,17 +5207,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5211,12 +5227,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5282,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,7 +5337,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5397,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5441,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5566,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5671,17 +5687,477 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
           <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5027,36 +5027,32 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5064,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5088,17 +5084,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5108,17 +5104,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5156,24 +5152,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5183,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5232,7 +5228,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5265,32 +5261,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,17 +5322,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5342,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5380,32 +5380,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5413,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5437,37 +5441,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -5495,32 +5499,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5528,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,37 +5560,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5610,32 +5618,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5643,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,17 +5679,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5687,12 +5699,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5758,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,7 +5809,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5812,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5929,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5988,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6103,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,15 +6159,475 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
         <is>
           <t>7/11</t>
         </is>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,22 +4746,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,22 +5099,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,22 +5456,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5509,24 +5509,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5737,32 +5737,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5770,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5794,17 +5798,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5814,12 +5818,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5852,32 +5856,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5885,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5909,37 +5917,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5967,32 +5975,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -6000,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6024,37 +6036,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6082,32 +6094,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6115,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6139,17 +6155,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6159,12 +6175,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6197,32 +6213,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6230,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6254,37 +6274,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6312,32 +6332,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6345,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6369,17 +6393,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6389,7 +6413,7 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6399,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6514,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6619,17 +6643,592 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>72.8</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>7/11</t>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,14 +2731,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,22 +3207,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,14 +3802,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,22 +4155,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,22 +4865,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,22 +4984,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,22 +5337,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,22 +5575,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,22 +5694,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5818,17 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6104,24 +6104,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,22 +6170,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6223,24 +6223,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6342,24 +6342,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,22 +6408,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -6451,32 +6451,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6484,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6508,37 +6512,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6566,32 +6570,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6599,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6623,17 +6631,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6643,17 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6681,32 +6689,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6714,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6738,37 +6750,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6944,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6983,7 +6995,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7059,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7174,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7223,12 +7235,702 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
           <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>71.8</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>71.2</t>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,14 +2136,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>71.8</t>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,14 +2374,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>71.2</t>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,14 +3445,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>71.8</t>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,14 +3683,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>71.2</t>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,17 +3802,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,14 +4274,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>71.8</t>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,14 +4512,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>71.2</t>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,22 +4746,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,22 +5099,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,17 +5461,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,14 +5813,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>71.8</t>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6294,17 +6294,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6532,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,14 +6646,14 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
           <t>71.8</t>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6808,32 +6808,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -6841,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6865,37 +6869,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6923,32 +6927,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6956,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6980,17 +6988,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -7000,7 +7008,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7038,32 +7046,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7071,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7095,37 +7107,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -7153,32 +7165,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7186,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7210,17 +7226,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7230,17 +7246,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -7268,32 +7284,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7301,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7325,32 +7345,32 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7383,32 +7403,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7416,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7440,17 +7464,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7460,17 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7570,7 +7594,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7646,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7700,7 +7724,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7810,7 +7834,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7876,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7920,17 +7944,707 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>71.6</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>75.2</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>8/11</t>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,17 +3326,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,14 +4155,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,17 +4274,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,17 +4393,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,14 +4984,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,17 +5218,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,22 +5575,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5699,17 +5699,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,17 +5813,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,22 +6408,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,14 +6527,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,17 +6646,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,17 +6770,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7175,19 +7175,19 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,14 +7479,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -7522,32 +7522,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7555,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,17 +7583,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7599,12 +7603,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7637,32 +7641,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7670,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7694,37 +7702,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -7752,32 +7760,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7785,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7809,17 +7821,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7829,17 +7841,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7867,32 +7879,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7900,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7924,32 +7940,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7982,32 +7998,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8015,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8039,32 +8059,32 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8130,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8245,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8284,7 +8304,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8360,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8399,7 +8419,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8475,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8519,12 +8539,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8590,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8644,7 +8664,697 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>71.7</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,17 +4155,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,22 +4746,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,17 +4984,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5104,17 +5104,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,17 +6170,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,17 +6527,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7127,17 +7127,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,17 +7479,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,17 +7598,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8008,24 +8008,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8117,32 +8117,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8150,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,17 +8178,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8194,17 +8198,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -8232,32 +8236,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8265,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8289,17 +8297,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8309,7 +8317,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8347,32 +8355,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8380,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8404,17 +8416,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8424,17 +8436,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -8462,32 +8474,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8495,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8519,32 +8535,32 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8577,32 +8593,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -8610,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8634,37 +8654,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -8692,32 +8712,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8725,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8749,17 +8773,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8769,12 +8793,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8807,32 +8831,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8840,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8864,32 +8892,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8955,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9004,12 +9032,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9109,7 +9137,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9185,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9229,7 +9257,7 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9300,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9344,17 +9372,477 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
           <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC79"/>
+  <dimension ref="A1:AC81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,17 +4398,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4517,17 +4517,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5818,17 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,17 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7960,17 +7960,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8079,17 +8079,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8317,17 +8317,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -8603,24 +8603,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8841,24 +8841,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8950,32 +8950,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8983,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9007,17 +9011,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9027,17 +9031,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -9065,32 +9069,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9098,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9122,17 +9130,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9142,17 +9150,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -9180,32 +9188,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9213,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9237,17 +9249,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9257,17 +9269,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -9295,32 +9307,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9328,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9352,27 +9368,27 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
@@ -9410,32 +9426,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -9443,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9467,17 +9487,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9487,7 +9507,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9558,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9597,7 +9617,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9612,7 +9632,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9722,7 +9742,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9788,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9832,15 +9852,245 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>75.9</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr">
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
         <is>
           <t>8/11</t>
         </is>

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7484,12 +7484,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9317,19 +9317,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9436,19 +9436,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9545,32 +9545,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9578,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,17 +9606,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9622,12 +9626,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9660,32 +9664,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9693,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9717,17 +9725,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9737,12 +9745,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9775,32 +9783,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9808,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9832,17 +9844,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9852,12 +9864,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9923,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9972,7 +9984,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10038,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10082,12 +10094,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">

--- a/data/export/2026-10-18-182路.xlsx
+++ b/data/export/2026-10-18-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9902,32 +9902,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9935,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9959,17 +9963,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9979,12 +9983,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10017,32 +10021,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10050,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10074,17 +10082,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10094,12 +10102,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
